--- a/artfynd/A 33546-2021 artfynd.xlsx
+++ b/artfynd/A 33546-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33546-2021 artfynd.xlsx
+++ b/artfynd/A 33546-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104023380</v>
+        <v>104023382</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544384.3906003602</v>
+        <v>544411</v>
       </c>
       <c r="R2" t="n">
-        <v>7093972.14957161</v>
+        <v>7093922</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104023382</v>
+        <v>104023383</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544410.612782607</v>
+        <v>544401</v>
       </c>
       <c r="R3" t="n">
-        <v>7093922.436936813</v>
+        <v>7093901</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104023386</v>
+        <v>104023385</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544382.1102951538</v>
+        <v>544390</v>
       </c>
       <c r="R4" t="n">
-        <v>7093977.828611411</v>
+        <v>7093959</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,11 +988,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1033,37 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104023385</v>
+        <v>104023381</v>
       </c>
       <c r="B5" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544390.2956976767</v>
+        <v>544339</v>
       </c>
       <c r="R5" t="n">
-        <v>7093959.053202</v>
+        <v>7094010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,6 +1099,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1149,15 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104023381</v>
+        <v>104023384</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544338.5396489582</v>
+        <v>544404</v>
       </c>
       <c r="R6" t="n">
-        <v>7094010.159998706</v>
+        <v>7093905</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1204,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,11 +1215,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1263,6 +1228,359 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104023377</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lilltjärnen-Stortjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>544403</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7093893</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104023386</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lilltjärnen-Stortjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>544382</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7093978</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104023380</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lilltjärnen-Stortjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>544384</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7093972</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
